--- a/output/variable_catalog.xlsx
+++ b/output/variable_catalog.xlsx
@@ -11,20 +11,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variable_Catalog" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_by_Group" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Availability" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readability_Formulas" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexicons_Seed" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collection_Plan" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References_to_Verify" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Your_List_Map" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readability_Formulas" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexicons_Seed" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collection_Plan" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References_to_Verify" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'README'!$A$1:$A$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Variable_Catalog'!$A$1:$L$359</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary_by_Group'!$A$1:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Availability'!$A$1:$D$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Readability_Formulas'!$A$1:$D$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Lexicons_Seed'!$A$1:$B$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Collection_Plan'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'References_to_Verify'!$A$1:$A$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Variable_Catalog'!$A$1:$L$437</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary_by_Group'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Availability'!$A$1:$D$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Your_List_Map'!$A$1:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Readability_Formulas'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Lexicons_Seed'!$A$1:$B$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Collection_Plan'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'References_to_Verify'!$A$1:$A$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +461,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>این کاتالوگ فهرست جامع متغیرها (غیر از مقاله ۱ و ۲) برای پژوهش‌های حسابداری/مالی روی شرکت‌های بورسی ایران است: 358 متغیر در 10 گروه.</t>
+          <t>این کاتالوگ فهرست جامع متغیرها (غیر از مقاله ۱ و ۲) برای پژوهش‌های حسابداری/مالی روی شرکت‌های بورسی ایران است: 436 متغیر در 13 گروه.</t>
         </is>
       </c>
     </row>
@@ -531,11 +533,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L359"/>
+  <dimension ref="A1:L437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
@@ -20862,8 +20864,4400 @@
         </is>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>قیمت و بازده</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>MK_PRICE_CLOSE</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>قیمت پایانی سال</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>آخرین قیمت پایانی سال مالی</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>جزئی</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K360" s="2" t="inlineStr"/>
+      <c r="L360" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>قیمت و بازده</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>MK_PRICE_HIGH</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>بیشترین قیمت سال</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>max قیمت روزانه</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K361" s="2" t="inlineStr"/>
+      <c r="L361" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>قیمت و بازده</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>MK_PRICE_LOW</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>کمترین قیمت سال</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>min قیمت روزانه</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K362" s="2" t="inlineStr"/>
+      <c r="L362" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>قیمت و بازده</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>MK_PRICE_MKT</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>قیمت/ارزش بازار</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>قیمت پایانی × تعداد سهام؛ ارزش روز</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>جزئی</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K363" s="2" t="inlineStr"/>
+      <c r="L363" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>قیمت و بازده</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>MK_RET_M_MEAN</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>میانگین بازده ماهانه</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>میانگین بازده ماه‌های شمسی در سال</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K364" s="2" t="inlineStr"/>
+      <c r="L364" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>قیمت و بازده</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>MK_RET_M_SD</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>انحراف معیار بازده ماهانه</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>σ بازده ماهانه</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K365" s="2" t="inlineStr"/>
+      <c r="L365" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>قیمت و بازده</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>MK_RET_ANN</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>بازده سالانه</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>از پنل (۱۲ و ۱۶ ماهه)</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K366" s="2" t="inlineStr"/>
+      <c r="L366" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>قیمت و بازده</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>MK_VOLAT</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>نوسان سالانه</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>σ بازده روزانه × √روزهای معاملاتی</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K367" s="2" t="inlineStr"/>
+      <c r="L367" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>قیمت و بازده</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>MK_BETA</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>بتای بازار</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>ضریب بازده شرکت روی شاخص کل (هفتگی/ماهانه)</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت) + شاخص کل</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K368" s="2" t="inlineStr"/>
+      <c r="L368" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>قیمت و بازده</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>MK_IDIOVOL</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>ریسک خاص شرکت</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>σ باقیمانده مدل بازار</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت) + شاخص کل</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K369" s="2" t="inlineStr"/>
+      <c r="L369" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>معاملات و نقدشوندگی</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>MK_VOL_SUM</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>حجم معاملات سال</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>مجموع حجم</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K370" s="2" t="inlineStr"/>
+      <c r="L370" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>معاملات و نقدشوندگی</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>MK_VOL_AVG</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>میانگین حجم معاملات</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>میانگین روزانه حجم</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K371" s="2" t="inlineStr"/>
+      <c r="L371" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>معاملات و نقدشوندگی</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>MK_VOL_DELTA</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>تغییر میانگین حجم</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>میانگین حجم سال جاری منهای سال قبل</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K372" s="2" t="inlineStr"/>
+      <c r="L372" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>معاملات و نقدشوندگی</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>MK_VAL_SUM</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>ارزش معاملات</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>مجموع ارزش ریالی</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K373" s="2" t="inlineStr"/>
+      <c r="L373" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>معاملات و نقدشوندگی</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>MK_TRADES_N</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>تعداد دفعات معاملات</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>مجموع تعداد معامله</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K374" s="2" t="inlineStr"/>
+      <c r="L374" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>معاملات و نقدشوندگی</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>MK_TRADE_DAYS</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>تعداد روزهای معاملاتی</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>روزهای دارای معامله</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K375" s="2" t="inlineStr"/>
+      <c r="L375" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>معاملات و نقدشوندگی</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>MK_ZERO_RET</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>روزهای بدون بازده</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>سهم روزهای بازده صفر</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K376" s="2" t="inlineStr">
+        <is>
+          <t>Lesmond et al. (1999)</t>
+        </is>
+      </c>
+      <c r="L376" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>معاملات و نقدشوندگی</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>MK_AMIHUD</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>عدم نقدشوندگی آمیهود</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>میانگین |بازده| ÷ ارزش معاملات</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K377" s="2" t="inlineStr">
+        <is>
+          <t>Amihud (2002)</t>
+        </is>
+      </c>
+      <c r="L377" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>معاملات و نقدشوندگی</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>MK_TURNOVER</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>گردش سهام</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>حجم ÷ تعداد سهام</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K378" s="2" t="inlineStr"/>
+      <c r="L378" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>معاملات و نقدشوندگی</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>MK_LIQ_RANK</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>رتبه نقدشوندگی</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>از پنل رهاورد</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K379" s="2" t="inlineStr"/>
+      <c r="L379" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>معاملات و نقدشوندگی</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>MK_HALT_DAYS</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>روزهای توقف/محدودیت</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>روزهای بدون معامله ناشی از توقف</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت)</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K380" s="2" t="inlineStr"/>
+      <c r="L380" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>اطلاعاتی بودن قیمت و ریسک سقوط</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>MK_SYNCH</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>همزمانی قیمت سهام</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>ln(R²/(1−R²)) از رگرسیون بازده شرکت روی بازده بازار و صنعت (هفتگی)</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت) + شاخص کل + شاخص صنعت</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K381" s="2" t="inlineStr">
+        <is>
+          <t>Morck et al. (2000)</t>
+        </is>
+      </c>
+      <c r="L381" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>اطلاعاتی بودن قیمت و ریسک سقوط</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>MK_R2</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>R² مدل بازار</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>ضریب تعیین خام</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت) + شاخص</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K382" s="2" t="inlineStr">
+        <is>
+          <t>Morck et al. (2000)</t>
+        </is>
+      </c>
+      <c r="L382" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>اطلاعاتی بودن قیمت و ریسک سقوط</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>MK_NCSKEW</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>چولگی منفی بازده</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>−[n(n−1)^{3/2}Σr³]÷[(n−1)(n−2)(Σr²)^{3/2}] روی باقیمانده‌های هفتگی</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت) + شاخص</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K383" s="2" t="inlineStr">
+        <is>
+          <t>Chen et al. (2001)</t>
+        </is>
+      </c>
+      <c r="L383" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>اطلاعاتی بودن قیمت و ریسک سقوط</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>MK_DUVOL</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>DUVOL</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>ln[(n_up−1)Σdown² ÷ (n_down−1)Σup²]</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت) + شاخص</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K384" s="2" t="inlineStr">
+        <is>
+          <t>Chen et al. (2001)</t>
+        </is>
+      </c>
+      <c r="L384" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>اطلاعاتی بودن قیمت و ریسک سقوط</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>MK_CRASH</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>ریسک سقوط (دامی)</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>۱ اگر بازده هفتگی ≤ میانگین −۳٫۰۹σ</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت) + شاخص</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K385" s="2" t="inlineStr">
+        <is>
+          <t>Hutton et al. (2009)</t>
+        </is>
+      </c>
+      <c r="L385" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>اطلاعاتی بودن قیمت و ریسک سقوط</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>MK_JUMP</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>جهش قیمت</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>۱ اگر بازده ≥ میانگین +۳٫۰۹σ</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: تاریخچه روزانه قیمت و معاملات هر نماد (یک درخواست برای هر شرکت) + شاخص</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K386" s="2" t="inlineStr">
+        <is>
+          <t>Kim et al. (2011)</t>
+        </is>
+      </c>
+      <c r="L386" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>اطلاعاتی بودن قیمت و ریسک سقوط</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>MK_PREDICT_ERR</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>خطای پیش‌بینی/Error</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>تعریف توسط کاربر (روشن شود: باقیمانده مدل؟ خطای پیش‌بینی سود؟)</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>دستی/خارجی</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K387" s="2" t="inlineStr"/>
+      <c r="L387" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>IND_CODE</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>صنعت (کد جزئی و کلی)</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>از پنل</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K388" s="2" t="inlineStr"/>
+      <c r="L388" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>IND_N</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>تعداد شرکت‌های صنعت</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>شمار شرکت‌های بورسی هر صنعت-سال در پنل</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K389" s="2" t="inlineStr"/>
+      <c r="L389" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>IND_SALES</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>فروش صنعت</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>Σ درآمد شرکت‌های صنعت-سال</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J390" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K390" s="2" t="inlineStr"/>
+      <c r="L390" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>IND_ASSETS</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>دارایی صنعت</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>Σ دارایی صنعت-سال</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K391" s="2" t="inlineStr"/>
+      <c r="L391" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>IND_SALES_GROWTH</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>رشد صنعت</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>رشد فروش صنعت (و جایگزین: بازده شاخص صنعت)</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K392" s="2" t="inlineStr"/>
+      <c r="L392" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>IND_INDEX</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>شاخص صنعت</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>ارزش/بازده شاخص صنعت سالانه</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC: شاخص‌های صنعت</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K393" s="2" t="inlineStr"/>
+      <c r="L393" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>IND_HHI_SALES</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>تمرکز صنعت (HHI فروش)</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>Σ(سهم فروش شرکت)² در صنعت-سال</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K394" s="2" t="inlineStr">
+        <is>
+          <t>Hou &amp; Robinson (2006)</t>
+        </is>
+      </c>
+      <c r="L394" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>IND_HHI_ASSETS</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>تمرکز صنعت (HHI دارایی)</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>Σ(سهم دارایی)²</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J395" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K395" s="2" t="inlineStr"/>
+      <c r="L395" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>IND_CR4</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>نسبت تمرکز ۴ شرکت بزرگ</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>سهم فروش ۴ شرکت بزرگ</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J396" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K396" s="2" t="inlineStr"/>
+      <c r="L396" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>IND_LERNER</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>شاخص لرنر</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>(فروش − بهای تمام‌شده − هزینه‌های عمومی و اداری) ÷ فروش (پروکسی مارک‌آپ)</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K397" s="2" t="inlineStr">
+        <is>
+          <t>Lerner (1934); Peress (2010)</t>
+        </is>
+      </c>
+      <c r="L397" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>IND_PCM</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>حاشیه سود بازار محصول</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>(فروش−COGS)÷فروش</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J398" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K398" s="2" t="inlineStr">
+        <is>
+          <t>Peress (2010)</t>
+        </is>
+      </c>
+      <c r="L398" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>IND_COMPET_ADJ</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>رقابت تعدیل‌شده</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>میانگین صنعت-سال LERNER</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J399" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K399" s="2" t="inlineStr"/>
+      <c r="L399" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>IND_POLITICAL</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>صنعت سیاسی</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>دامی صنایع تحت نظارت/حمایت دولت (طبقه‌بندی پژوهشگر؛ باید تعریف و توجیه شود)</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>قضاوت پژوهشگر/فهرست خارجی</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>دستی/خارجی</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K400" s="2" t="inlineStr"/>
+      <c r="L400" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>ویژگی‌های صنعت (از پنل کل بازار)</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>IND_REGULATED</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>صنعت تنظیم‌شده</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>قیمت‌گذاری دستوری/انرژی‌بر/صادرات‌محور (دامی)</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>قضاوت پژوهشگر</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>دستی/خارجی</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J401" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K401" s="2" t="inlineStr"/>
+      <c r="L401" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>۱۳) ارز و تکالیف دولتی (ویژه ایران)</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>ارز ترجیحی</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>FX_ANY</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>دریافت ارز ترجیحی</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>۱ اگر شرکت ارز با نرخ ترجیحی/مرجع/نیما دریافت کرده</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>گزارش هیئت مدیره/یادداشت‌ها (متن) + فهرست بانک مرکزی (خارجی)</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr">
+        <is>
+          <t>پایین؛ منبع رسمی لازم</t>
+        </is>
+      </c>
+      <c r="K402" s="2" t="inlineStr"/>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>۱۳) ارز و تکالیف دولتی (ویژه ایران)</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>ارز ترجیحی</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>FX_REF</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>ارز مرجع</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>۱ اگر ارز مرجع (۴۲۰۰ تومانی/ترجیحی) دریافت کرده</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>همان</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K403" s="2" t="inlineStr"/>
+      <c r="L403" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>۱۳) ارز و تکالیف دولتی (ویژه ایران)</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>ارز ترجیحی</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>FX_NIMA</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>ارز نیمایی</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>۱ اگر ارز نیمایی دریافت کرده</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>همان</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K404" s="2" t="inlineStr"/>
+      <c r="L404" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>۱۳) ارز و تکالیف دولتی (ویژه ایران)</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>ارز ترجیحی</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>FX_AMOUNT</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>مبلغ ارز دریافتی</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>از یادداشت/گزارش در صورت افشا</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>یادداشت‌ها/گزارش</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K405" s="2" t="inlineStr"/>
+      <c r="L405" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>۱۳) ارز و تکالیف دولتی (ویژه ایران)</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>ارز ترجیحی</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>FX_EXPOSURE</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>ریسک ارزی</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>بدهی/دارایی ارزی ÷ دارایی (یادداشت دارایی‌ها و بدهی‌های ارزی)</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>یادداشت‌ها</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J406" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K406" s="2" t="inlineStr"/>
+      <c r="L406" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>۱۳) ارز و تکالیف دولتی (ویژه ایران)</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>ارز ترجیحی</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>FX_GAIN</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>سود و زیان تسعیر</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>ستون سود و زیان تسعیر</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K407" s="2" t="inlineStr"/>
+      <c r="L407" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>کمیته حسابرسی: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>AC_NONEXEC_N</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>اعضای غیرموظف کمیته</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>تعداد</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت هیئت مدیره / اطلاعات اعضای هیئت مدیره (کدال)</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K408" s="2" t="inlineStr"/>
+      <c r="L408" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>کمیته حسابرسی: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>AC_NONEXEC_RATIO</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>نسبت غیرموظف به کل کمیته</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>AC_NONEXEC_N÷AC_SIZE</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت هیئت مدیره / اطلاعات اعضای هیئت مدیره (کدال)</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K409" s="2" t="inlineStr"/>
+      <c r="L409" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>کمیته حسابرسی: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>AC_INDEP_N</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>اعضای مستقل کمیته</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>تعداد</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت هیئت مدیره / اطلاعات اعضای هیئت مدیره (کدال)</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K410" s="2" t="inlineStr"/>
+      <c r="L410" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>کمیته حسابرسی: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>AC_FINEXP_N</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>اعضای دارای تخصص مالی</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>تعداد (از رزومه/تحصیلات)</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت هیئت مدیره / اطلاعات اعضای هیئت مدیره (کدال)</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J411" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K411" s="2" t="inlineStr"/>
+      <c r="L411" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>کمیته حسابرسی: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>AC_PROFCERT_N</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>اعضای دارای مدرک حرفه‌ای</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>تعداد (حسابدار رسمی، CPA، ACCA، CFA ...)</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>مدارک اعضا (دستی)</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>دستی/خارجی</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J412" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K412" s="2" t="inlineStr"/>
+      <c r="L412" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>کمیته حسابرسی: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>AC_CERT_TYPES</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>نوع مدارک اعضای کمیته</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>فهرست مدارک</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>مدارک اعضا (دستی)</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>دستی/خارجی</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J413" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K413" s="2" t="inlineStr"/>
+      <c r="L413" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>کمیته حسابرسی: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>AC_FINEXP_SHARE</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>سهم متخصصان مالی کمیته</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>AC_FINEXP_N÷AC_SIZE</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت هیئت مدیره / اطلاعات اعضای هیئت مدیره (کدال)</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J414" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K414" s="2" t="inlineStr"/>
+      <c r="L414" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>هیئت مدیره و مدیرعامل: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>CEO_NAME</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>نام مدیرعامل</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>رشته متنی (کلید برای CEO_CHANGE و سابقه)</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>اطلاعات اعضای هیئت مدیره/گزارش</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J415" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K415" s="2" t="inlineStr"/>
+      <c r="L415" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>هیئت مدیره و مدیرعامل: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>CEO_NOCHANGE</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>عدم تغییر مدیرعامل</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>۱ − CEO_CHANGE (یا نام سال t = نام t−1)</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>نام مدیرعامل چندساله</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J416" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K416" s="2" t="inlineStr"/>
+      <c r="L416" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>هیئت مدیره و مدیرعامل: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>CEO_CHAIR_OR_VICE</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>مدیرعامل رئیس یا نایب رئیس</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>۱ اگر مدیرعامل رئیس/نایب رئیس هیئت</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت هیئت مدیره / اطلاعات اعضای هیئت مدیره (کدال)</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J417" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K417" s="2" t="inlineStr"/>
+      <c r="L417" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>هیئت مدیره و مدیرعامل: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>BD_EXEC_N</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>تعداد اعضای موظف</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr"/>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت هیئت مدیره / اطلاعات اعضای هیئت مدیره (کدال)</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J418" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K418" s="2" t="inlineStr"/>
+      <c r="L418" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>هیئت مدیره و مدیرعامل: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>BD_NONEXEC_N</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>تعداد اعضای غیرموظف</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr"/>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت هیئت مدیره / اطلاعات اعضای هیئت مدیره (کدال)</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J419" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K419" s="2" t="inlineStr"/>
+      <c r="L419" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>هیئت مدیره و مدیرعامل: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>BD_NONEXEC_RATIO</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>نسبت اعضای غیرموظف</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>BD_NONEXEC_N÷BD_SIZE</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت هیئت مدیره / اطلاعات اعضای هیئت مدیره (کدال)</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J420" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K420" s="2" t="inlineStr"/>
+      <c r="L420" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>هیئت مدیره و مدیرعامل: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>BD_MONITOR</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>نظارت هیئت مدیره</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>تعریف شما؟ پیشنهاد: ترکیب جلسات، استقلال، کمیته‌ها (PCA) یا شاخص نظارتی از متن</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت هیئت مدیره / اطلاعات اعضای هیئت مدیره (کدال)</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J421" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K421" s="2" t="inlineStr"/>
+      <c r="L421" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>هیئت مدیره و مدیرعامل: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>BD_FINEXP_N</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>اعضای هیئت دارای دانش مالی</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>تعداد</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت هیئت مدیره / اطلاعات اعضای هیئت مدیره (کدال)</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J422" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K422" s="2" t="inlineStr"/>
+      <c r="L422" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>هیئت مدیره و مدیرعامل: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>BD_FEMALE_N</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>تعداد زن در هیئت</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr"/>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت هیئت مدیره / اطلاعات اعضای هیئت مدیره (کدال)</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J423" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K423" s="2" t="inlineStr"/>
+      <c r="L423" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>هیئت مدیره و مدیرعامل: جزئیات تکمیلی</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>OWN_MGR_DETAIL</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>مالکیت مدیریتی</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>درصد سهام اعضای هیئت‌مدیره و مدیرعامل</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>سهامداران</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J424" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K424" s="2" t="inlineStr"/>
+      <c r="L424" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>SUB_EXIST</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>شرکت فرعی دارد؟</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>۱ اگر صورت مالی تلفیقی/یادداشت شرکت‌های فرعی</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>یادداشت‌ها/صورت تلفیقی</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J425" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K425" s="2" t="inlineStr"/>
+      <c r="L425" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>SUB_N</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>تعداد شرکت‌های فرعی</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr"/>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>یادداشت‌ها</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J426" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K426" s="2" t="inlineStr"/>
+      <c r="L426" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>EXPORT_SALES</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>فروش خارجی دارد؟</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>۱ اگر فروش صادراتی در یادداشت/گزارش</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>یادداشت‌ها</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J427" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K427" s="2" t="inlineStr"/>
+      <c r="L427" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>EXPORT_SHARE</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>سهم فروش خارجی</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>فروش صادراتی÷فروش</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>یادداشت‌ها</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I428" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J428" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K428" s="2" t="inlineStr"/>
+      <c r="L428" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>SEG_GEO_N</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>تعداد بخش‌های جغرافیایی</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>تعداد بخش‌های گزارش شده</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>یادداشت اطلاعات بخشی</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J429" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K429" s="2" t="inlineStr"/>
+      <c r="L429" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>SEG_BUS_N</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>تعداد بخش‌های عملیاتی</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr"/>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>یادداشت اطلاعات بخشی</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J430" s="2" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="K430" s="2" t="inlineStr"/>
+      <c r="L430" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_N</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>تعداد اخبار</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>تعریف شما؟ پیشنهاد: تعداد نامه‌های کدال در سال (DISC_N_LETTERS)؛ یا اخبار سایت‌های خبری (خارجی)</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>عنوان نامه‌ها / خارجی</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>عنوان نامه‌های کدال</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J431" s="2" t="inlineStr">
+        <is>
+          <t>بالا برای نامه‌ها</t>
+        </is>
+      </c>
+      <c r="K431" s="2" t="inlineStr"/>
+      <c r="L431" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>AUD_MODIFIED</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>اظهارنظر تعدیل‌شده</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>۱ اگر مشروط/مردود/عدم اظهارنظر</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>گزارش حسابرس</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J432" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K432" s="2" t="inlineStr"/>
+      <c r="L432" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>AUD_RANK</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>رتبه موسسه حسابرسی</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>رتبه رسمی (جامعه حسابداران رسمی/سازمان بورس) — جدول خارجی</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>فهرست رسمی (دستی)</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>دستی/خارجی</t>
+        </is>
+      </c>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J433" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K433" s="2" t="inlineStr"/>
+      <c r="L433" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>AUD_TYPE</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>نوع حسابرس</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>سازمان حسابرسی/موسسه خصوصی/بزرگ؛ دامی‌ها</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>گزارش حسابرس</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>متن‌کاوی خودکار</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J434" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K434" s="2" t="inlineStr"/>
+      <c r="L434" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>FY_GREG</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>سال مالی میلادی</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>سال شمسی + ۶۲۱ (پایان ۲۹ اسفند)</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J435" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K435" s="2" t="inlineStr"/>
+      <c r="L435" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>FIRM_FOUND_DATE</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>تاریخ تأسیس</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>از صفحه مشخصات شرکت در کدال/TSETMC؛ AGE = سال − سال تأسیس</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>کدال: مشخصات شرکت</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="J436" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="K436" s="2" t="inlineStr"/>
+      <c r="L436" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>۴) حاکمیت شرکتی</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>ساختار شرکت و فعالیت بین‌المللی (از یادداشت‌ها)</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>SGA_RATIO</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>هزینه اداری و عمومی</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>هزینه عمومی و اداری ÷ فروش</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>پنل صورت‌های مالی فعلی</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>ساختاریافته (پنل صورت مالی)</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="J437" s="2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="K437" s="2" t="inlineStr"/>
+      <c r="L437" s="2" t="inlineStr">
+        <is>
+          <t>فقط ویژگی (سند نگه‌داری نمی‌شود)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L359"/>
+  <autoFilter ref="A1:L437"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20874,10 +25268,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
@@ -20976,230 +25370,305 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>۲) زمان‌بندی و رفتار گزارشدهی</t>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>۳) کیفیت سود و گزارشگری مالی</t>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G5" s="2" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>۴) حاکمیت شرکتی</t>
+          <t>۱۳) ارز و تکالیف دولتی (ویژه ایران)</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>31</v>
-      </c>
       <c r="G6" s="2" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>۵) گزارشگری پایداری (ESG)</t>
+          <t>۲) زمان‌بندی و رفتار گزارشدهی</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>۶) مسئولیت اجتماعی (CSR)</t>
+          <t>۳) کیفیت سود و گزارشگری مالی</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>۷) مالی رفتاری</t>
+          <t>۴) حاکمیت شرکتی</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>35</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>۸) فناوری و نوآوری</t>
+          <t>۵) گزارشگری پایداری (ESG)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="E10" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="G10" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>۹) سرمایه انسانی</t>
+          <t>۶) مسئولیت اجتماعی (CSR)</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>۷) مالی رفتاری</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>۸) فناوری و نوآوری</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>۹) سرمایه انسانی</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>کل</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>358</v>
+      <c r="B15" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>436</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21210,10 +25679,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -21276,138 +25745,1178 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>۲) زمان‌بندی و رفتار گزارشدهی</t>
+          <t>۱۱) بازار و معاملات سهام (TSETMC)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>۳) کیفیت سود و گزارشگری مالی</t>
+          <t>۱۲) صنعت و رقابت بازار محصول</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>۴) حاکمیت شرکتی</t>
+          <t>۱۳) ارز و تکالیف دولتی (ویژه ایران)</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>۵) گزارشگری پایداری (ESG)</t>
+          <t>۲) زمان‌بندی و رفتار گزارشدهی</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>۶) مسئولیت اجتماعی (CSR)</t>
+          <t>۳) کیفیت سود و گزارشگری مالی</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>۷) مالی رفتاری</t>
+          <t>۴) حاکمیت شرکتی</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>21</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>۸) فناوری و نوآوری</t>
+          <t>۵) گزارشگری پایداری (ESG)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>۶) مسئولیت اجتماعی (CSR)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>۷) مالی رفتاری</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>۸) فناوری و نوآوری</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>۹) سرمایه انسانی</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D14" s="2" t="n">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D11"/>
+  <autoFilter ref="A1:D14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>متغیر درخواستی شما</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>کد در کاتالوگ</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>منبع</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>نکته/محدودیت</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>نام مدیرعامل</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>CEO_NAME</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>کدال: اطلاعات اعضای هیئت مدیره/گزارش</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌خودکار؛ بدون ذخیره سند</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>عدم تغییر مدیرعامل</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CEO_NOCHANGE (و CEO_CHANGE)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>جدید/موجود</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>عنوان نامه‌ها یا مقایسه نام سال‌ها</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>خودکار از عنوان نامه‌ها</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری نهادی؛ مالکیت نهادی؛ INOW</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>OWN_INST</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>موجود</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC/کدال سهامداران</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>نیازمند طبقه‌بندی نام‌ها با فهرست؛ سری سالانه از نامه‌های ترکیب سهامداران</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>بالاترین سهام</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>OWN_TOP1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>موجود</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC/کدال</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>تعداد اخبار</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_N</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>نیازمند تعریف</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>عنوان نامه‌های کدال یا اخبار خارجی</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>تعریف را مشخص کنید: نامه‌های کدال یا سایت خبری؟</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ارز نیمایی/مرجع دریافت کرده؛ آیا ارز دریافت کرده</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>FX_NIMA, FX_REF, FX_ANY</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>متن گزارش/یادداشت + فهرست رسمی بانک مرکزی</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>ضعف: داده رسمی ساختاریافته در کدال نیست؛ پایین‌ترین اعتماد</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>همزمانی قیمت سهام</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>MK_SYNCH, MK_R2</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC روزانه + شاخص کل + شاخص صنعت</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>کم‌هزینه: یک درخواست برای هر شرکت</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>چولگی منفی بازده سهام</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>MK_NCSKEW, MK_DUVOL, MK_CRASH</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC روزانه (تجمیع هفتگی)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>نیازمند بازده هفتگی؛ پنل فعلی ندارد</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>میانگین و انحراف معیار بازده ماهانه</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>MK_RET_M_MEAN, MK_RET_M_SD</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC روزانه</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>صنعت؛ شاخص صنعت؛ رشد صنعت</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>IND_CODE, IND_INDEX, IND_SALES_GROWTH</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>جدید/موجود</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>پنل + شاخص صنعت TSETMC</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>رشد صنعت از فروش پنل بدون جمع‌آوری</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>دارایی صنعت؛ فروش صنعت؛ تعداد شرکت‌های صنعت</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>IND_ASSETS, IND_SALES, IND_N</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>پنل کل بازار (محاسبه)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>بدون جمع‌آوری؛ از پنل ۷۳۷ شرکتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>صنعت سیاسی</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>IND_POLITICAL</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>طبقه‌بندی پژوهشگر</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>باید تعریف شود (مثلاً صنایع تحت قیمت‌گذاری دستوری)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>سال مالی؛ سال مالی میلادی</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>FY_GREG</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>پنل</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>محاسبه ساده</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>MK_PREDICT_ERR</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>نیازمند تعریف</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>روشن کنید این خطا چیست</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>تاریخ گزارش حسابرس؛ تأخیر گزارش حسابرسی</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>AUD_DATE, AUD_LAG</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>موجود</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>گزارش حسابرس</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>نام حسابرس/موسسه؛ اسم حسابرس</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>AUD_FIRM</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>موجود</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>گزارش حسابرس</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>رتبه حسابرس</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>AUD_RANK (+AUD_SIZE پروکسی)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>فهرست رسمی رتبه‌بندی (خارجی)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>جدول رتبه‌ها را خودتان تهیه کنید؛ پروکسی: اندازه</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>اظهارنظر حسابرس تعدیل‌شده؛ Audittype</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>AUD_MODIFIED, AUD_TYPE</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>موجود/جدید</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>گزارش حسابرس</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Audittype را تعریف کنید</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>حق‌الزحمه حسابرس</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>AUD_FEE</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>موجود</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>گزارش هیئت مدیره</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌خودکار؛ همیشه افشا نمی‌شود</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>دوره تصدی؛ اندازه حسابرس</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>AUD_TENURE, AUD_SIZE</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>موجود</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>ترکیبی</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ضعف کنترل داخلی؛ نقاط ضعف (تعداد بند شرط)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>IC_WEAK, AUD_ITEMS_N</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>موجود</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>گزارش کنترل داخلی + حسابرس</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>کمیته حسابرسی: وجود، اندازه، جلسات، استقلال، تخصص مالی، اعضای غیرموظف/مستقل/متخصص/مدارک</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>AC_EXIST, AC_SIZE, AC_MEET, AC_INDEP, AC_FINEXP, AC_NONEXEC_N, AC_INDEP_N, AC_FINEXP_N, AC_PROFCERT_N, AC_CERT_TYPES</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>موجود/جدید</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>گزارش هیئت مدیره</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>اعضا و مدارک: نیمه‌دستی/دستی با کمترین دقت</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>اندازه، استقلال، موظف/غیرموظف، زنان، دانش مالی هیئت مدیره</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>BD_SIZE, BD_INDEP, BD_EXEC_N, BD_NONEXEC_N/RATIO, BD_FEMALE_N, BD_FINEXP_N</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>موجود/جدید</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>گزارش هیئت مدیره</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>مدیرعامل رئیس یا نایب رئیس؛ دوگانگی وظیفه</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>CEO_CHAIR_OR_VICE, BD_DUALITY</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>موجود/جدید</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>گزارش هیئت مدیره</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>نظارت هیئت مدیره</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>BD_MONITOR</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>نیازمند تعریف</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>گزارش هیئت مدیره</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>تعریف را مشخص کنید</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>مالکیت مدیریت</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>OWN_MGR</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>موجود</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>سهامداران + اعضا</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>نیمه‌دستی</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>شرکت فرعی دارد؟</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SUB_EXIST, SUB_N</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>یادداشت‌ها</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>فروش خارجی/صادراتی؛ عملیات فرامرزی</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>EXPORT_SALES, EXPORT_SHARE, FIRM_FOREIGN_OPS</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>جدید/موجود</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>یادداشت‌ها/گزارش</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>تعداد بخش‌های جغرافیایی (seg)</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SEG_GEO_N, SEG_BUS_N</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>یادداشت اطلاعات بخشی</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>حجم، ارزش، تعداد دفعات، روز معاملاتی، قیمت‌ها، تغییر حجم</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>MK_VOL_*, MK_VAL_SUM, MK_TRADES_N, MK_TRADE_DAYS, MK_PRICE_*</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>TSETMC روزانه</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>کم‌هزینه</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>HHI</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>IND_HHI_SALES (رقابت) و OWN_HHI (مالکیت)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>جدید/موجود</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>پنل / TSETMC</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>مشخص کنید کدام HHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>LERNER</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>IND_LERNER</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>پنل</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>محاسبه از پنل بدون جمع‌آوری</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>مدیریت سود</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>DA_JONES, DA_MJONES, DA_KLW, AQ_DD, REM_*</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>موجود</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>پنل</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>بدون جمع‌آوری</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>هزینه‌های اداری و عمومی؛ جریان نقد عملیاتی (CFO)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SGA_RATIO, CFO_TA</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>جدید/موجود</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>پنل</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>RD_EXP, RD_INTENS</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>موجود</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>یادداشت‌ها</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>اغلب افشا نمی‌شود؛ پوشش کم</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>تاریخ تأسیس؛ AGE</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>FIRM_FOUND_DATE, FIRM_AGE</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>جدید</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>کدال: مشخصات شرکت</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>آیا تجدید ارائه شده است؟</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>RESTATE</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>موجود</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>پنل</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E38"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21772,7 +27281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22019,7 +27528,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22234,13 +27743,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A95"/>
+  <dimension ref="A1:A103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -22277,642 +27786,698 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Ashbaugh-Skaife, H., Collins, D. W., &amp; Kinney, W. R. (2007). The discovery and reporting of internal control deficiencies prior to SOX-mandated audits. Journal of Accounting and Economics, 44(1–2), 166–192.</t>
+          <t>Amihud, Y. (2002). Illiquidity and stock returns: Cross-section and time-series effects. Journal of Financial Markets, 5(1), 31–56.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Ball, R., &amp; Shivakumar, L. (2005). Earnings quality in UK private firms. Journal of Accounting and Economics, 39(1), 83–128.</t>
+          <t>Ashbaugh-Skaife, H., Collins, D. W., &amp; Kinney, W. R. (2007). The discovery and reporting of internal control deficiencies prior to SOX-mandated audits. Journal of Accounting and Economics, 44(1–2), 166–192.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Ball, R., Kothari, S. P., &amp; Robin, A. (2000). The effect of international institutional factors on properties of accounting earnings. Journal of Accounting and Economics, 29(1), 1–51.</t>
+          <t>Ball, R., &amp; Shivakumar, L. (2005). Earnings quality in UK private firms. Journal of Accounting and Economics, 39(1), 83–128.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Barth, M. E., Landsman, W. R., &amp; Lang, M. H. (2008). International accounting standards and accounting quality. Journal of Accounting Research, 46(3), 467–498.</t>
+          <t>Ball, R., Kothari, S. P., &amp; Robin, A. (2000). The effect of international institutional factors on properties of accounting earnings. Journal of Accounting and Economics, 29(1), 1–51.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Basu, S. (1997). The conservatism principle and the asymmetric timeliness of earnings. Journal of Accounting and Economics, 24(1), 3–37.</t>
+          <t>Barth, M. E., Landsman, W. R., &amp; Lang, M. H. (2008). International accounting standards and accounting quality. Journal of Accounting Research, 46(3), 467–498.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Beasley, M. S. (1996). An empirical analysis of the relation between the board of director composition and financial statement fraud. The Accounting Review, 71(4), 443–465.</t>
+          <t>Basu, S. (1997). The conservatism principle and the asymmetric timeliness of earnings. Journal of Accounting and Economics, 24(1), 3–37.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Beaver, W. H., &amp; Ryan, S. G. (2000). Biases and lags in book value and their effects on the ability of the book-to-market ratio to predict book return on equity. Journal of Accounting Research, 38(1), 127–148.</t>
+          <t>Beasley, M. S. (1996). An empirical analysis of the relation between the board of director composition and financial statement fraud. The Accounting Review, 71(4), 443–465.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Beneish, M. D. (1999). The detection of earnings manipulation. Financial Analysts Journal, 55(5), 24–36.</t>
+          <t>Beaver, W. H., &amp; Ryan, S. G. (2000). Biases and lags in book value and their effects on the ability of the book-to-market ratio to predict book return on equity. Journal of Accounting Research, 38(1), 127–148.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Bettman, J. R., &amp; Weitz, B. A. (1983). Attributions in the board room: Causal reasoning in corporate annual reports. Administrative Science Quarterly, 28(2), 165–183.</t>
+          <t>Beneish, M. D. (1999). The detection of earnings manipulation. Financial Analysts Journal, 55(5), 24–36.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Björnsson, C. H. (1968). Läsbarhet. Stockholm: Liber.</t>
+          <t>Bettman, J. R., &amp; Weitz, B. A. (1983). Attributions in the board room: Causal reasoning in corporate annual reports. Administrative Science Quarterly, 28(2), 165–183.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Bonsall, S. B., Leone, A. J., Miller, B. P., &amp; Rennekamp, K. (2017). A plain English measure of financial reporting readability. Journal of Accounting and Economics, 63(2–3), 329–357.</t>
+          <t>Björnsson, C. H. (1968). Läsbarhet. Stockholm: Liber.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Botosan, C. A. (1997). Disclosure level and the cost of equity capital. The Accounting Review, 72(3), 323–349.</t>
+          <t>Bonsall, S. B., Leone, A. J., Miller, B. P., &amp; Rennekamp, K. (2017). A plain English measure of financial reporting readability. Journal of Accounting and Economics, 63(2–3), 329–357.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Brown, L. D., &amp; Caylor, M. L. (2006). Corporate governance and firm valuation. Journal of Accounting and Public Policy, 25(4), 409–434.</t>
+          <t>Botosan, C. A. (1997). Disclosure level and the cost of equity capital. The Accounting Review, 72(3), 323–349.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Brown, W. O., Helland, E., &amp; Smith, J. K. (2006). Corporate philanthropic practices. Journal of Corporate Finance, 12(5), 855–877.</t>
+          <t>Brown, L. D., &amp; Caylor, M. L. (2006). Corporate governance and firm valuation. Journal of Accounting and Public Policy, 25(4), 409–434.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Burgstahler, D., &amp; Dichev, I. (1997). Earnings management to avoid earnings decreases and losses. Journal of Accounting and Economics, 24(1), 99–126.</t>
+          <t>Brown, W. O., Helland, E., &amp; Smith, J. K. (2006). Corporate philanthropic practices. Journal of Corporate Finance, 12(5), 855–877.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Chan, L. K. C., Lakonishok, J., &amp; Sougiannis, T. (2001). The stock market valuation of research and development expenditures. Journal of Finance, 56(6), 2431–2456.</t>
+          <t>Burgstahler, D., &amp; Dichev, I. (1997). Earnings management to avoid earnings decreases and losses. Journal of Accounting and Economics, 24(1), 99–126.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Chatterjee, A., &amp; Hambrick, D. C. (2007). It's all about me: Narcissistic chief executive officers and their effects on company strategy and performance. Administrative Science Quarterly, 52(3), 351–386.</t>
+          <t>Chan, L. K. C., Lakonishok, J., &amp; Sougiannis, T. (2001). The stock market valuation of research and development expenditures. Journal of Finance, 56(6), 2431–2456.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Cho, C. H., &amp; Patten, D. M. (2007). The role of environmental disclosures as tools of legitimacy. Accounting, Organizations and Society, 32(7–8), 639–647.</t>
+          <t>Chatterjee, A., &amp; Hambrick, D. C. (2007). It's all about me: Narcissistic chief executive officers and their effects on company strategy and performance. Administrative Science Quarterly, 52(3), 351–386.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Claessens, S., Djankov, S., &amp; Lang, L. H. P. (2000). The separation of ownership and control in East Asian corporations. Journal of Financial Economics, 58(1–2), 81–112.</t>
+          <t>Chen, J., Hong, H., &amp; Stein, J. C. (2001). Forecasting crashes: Trading volume, past returns, and conditional skewness in stock prices. Journal of Financial Economics, 61(3), 345–381.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Clarkson, P. M., Li, Y., Richardson, G. D., &amp; Vasvari, F. P. (2008). Revisiting the relation between environmental performance and environmental disclosure. Accounting, Organizations and Society, 33(4–5), 303–327.</t>
+          <t>Cho, C. H., &amp; Patten, D. M. (2007). The role of environmental disclosures as tools of legitimacy. Accounting, Organizations and Society, 32(7–8), 639–647.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Cohen, D. A., &amp; Zarowin, P. (2010). Accrual-based and real earnings management activities around seasoned equity offerings. Journal of Accounting and Economics, 50(1), 2–19.</t>
+          <t>Claessens, S., Djankov, S., &amp; Lang, L. H. P. (2000). The separation of ownership and control in East Asian corporations. Journal of Financial Economics, 58(1–2), 81–112.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Coleman, M., &amp; Liau, T. L. (1975). A computer readability formula designed for machine scoring. Journal of Applied Psychology, 60(2), 283–284.</t>
+          <t>Clarkson, P. M., Li, Y., Richardson, G. D., &amp; Vasvari, F. P. (2008). Revisiting the relation between environmental performance and environmental disclosure. Accounting, Organizations and Society, 33(4–5), 303–327.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Core, J. E., Holthausen, R. W., &amp; Larcker, D. F. (1999). Corporate governance, chief executive officer compensation, and firm performance. Journal of Financial Economics, 51(3), 371–406.</t>
+          <t>Cohen, D. A., &amp; Zarowin, P. (2010). Accrual-based and real earnings management activities around seasoned equity offerings. Journal of Accounting and Economics, 50(1), 2–19.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Craswell, A. T., Francis, J. R., &amp; Taylor, S. L. (1995). Auditor brand name reputations and industry specializations. Journal of Accounting and Economics, 20(3), 297–322.</t>
+          <t>Coleman, M., &amp; Liau, T. L. (1975). A computer readability formula designed for machine scoring. Journal of Applied Psychology, 60(2), 283–284.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DeAngelo, L. E. (1981). Auditor size and audit quality. Journal of Accounting and Economics, 3(3), 183–199.</t>
+          <t>Core, J. E., Holthausen, R. W., &amp; Larcker, D. F. (1999). Corporate governance, chief executive officer compensation, and firm performance. Journal of Financial Economics, 51(3), 371–406.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>DeFond, M. L., Hann, R. N., &amp; Hu, X. (2005). Does the market value financial expertise on audit committees of boards of directors? Journal of Accounting Research, 43(2), 153–193.</t>
+          <t>Craswell, A. T., Francis, J. R., &amp; Taylor, S. L. (1995). Auditor brand name reputations and industry specializations. Journal of Accounting and Economics, 20(3), 297–322.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DeHaan, E., Shevlin, T., &amp; Thornock, J. (2015). Market (in)attention and the strategic scheduling and timing of earnings announcements. Journal of Accounting and Economics, 60(1), 36–55.</t>
+          <t>DeAngelo, L. E. (1981). Auditor size and audit quality. Journal of Accounting and Economics, 3(3), 183–199.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Dechow, P. M., &amp; Dichev, I. D. (2002). The quality of accruals and earnings. The Accounting Review, 77(Supplement), 35–59.</t>
+          <t>DeFond, M. L., Hann, R. N., &amp; Hu, X. (2005). Does the market value financial expertise on audit committees of boards of directors? Journal of Accounting Research, 43(2), 153–193.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Dechow, P. M., Ge, W., Larson, C. R., &amp; Sloan, R. G. (2011). Predicting material accounting misstatements. Contemporary Accounting Research, 28(1), 17–82.</t>
+          <t>DeHaan, E., Shevlin, T., &amp; Thornock, J. (2015). Market (in)attention and the strategic scheduling and timing of earnings announcements. Journal of Accounting and Economics, 60(1), 36–55.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Dechow, P. M., Sloan, R. G., &amp; Sweeney, A. P. (1995). Detecting earnings management. The Accounting Review, 70(2), 193–225.</t>
+          <t>Dechow, P. M., &amp; Dichev, I. D. (2002). The quality of accruals and earnings. The Accounting Review, 77(Supplement), 35–59.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Dechow, P. M., Sloan, R. G., &amp; Sweeney, A. P. (1996). Causes and consequences of earnings manipulation. Contemporary Accounting Research, 13(1), 1–36.</t>
+          <t>Dechow, P. M., Ge, W., Larson, C. R., &amp; Sloan, R. G. (2011). Predicting material accounting misstatements. Contemporary Accounting Research, 28(1), 17–82.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Dhaliwal, D. S., Li, O. Z., Tsang, A., &amp; Yang, Y. G. (2011). Voluntary nonfinancial disclosure and the cost of equity capital. The Accounting Review, 86(1), 59–100.</t>
+          <t>Dechow, P. M., Sloan, R. G., &amp; Sweeney, A. P. (1995). Detecting earnings management. The Accounting Review, 70(2), 193–225.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Dichev, I. D., &amp; Tang, V. W. (2009). Earnings volatility and earnings predictability. Journal of Accounting and Economics, 47(1–2), 160–181.</t>
+          <t>Dechow, P. M., Sloan, R. G., &amp; Sweeney, A. P. (1996). Causes and consequences of earnings manipulation. Contemporary Accounting Research, 13(1), 1–36.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Doyle, J., Ge, W., &amp; McVay, S. (2007). Determinants of weaknesses in internal control over financial reporting. Journal of Accounting and Economics, 44(1–2), 193–223.</t>
+          <t>Dhaliwal, D. S., Li, O. Z., Tsang, A., &amp; Yang, Y. G. (2011). Voluntary nonfinancial disclosure and the cost of equity capital. The Accounting Review, 86(1), 59–100.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Dyreng, S. D., Hanlon, M., &amp; Maydew, E. L. (2008). Long-run corporate tax avoidance. The Accounting Review, 83(1), 61–82.</t>
+          <t>Dichev, I. D., &amp; Tang, V. W. (2009). Earnings volatility and earnings predictability. Journal of Accounting and Economics, 47(1–2), 160–181.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Edmans, A. (2011). Does the stock market fully value intangibles? Employee satisfaction and equity prices. Journal of Financial Economics, 101(3), 621–640.</t>
+          <t>Doyle, J., Ge, W., &amp; McVay, S. (2007). Determinants of weaknesses in internal control over financial reporting. Journal of Accounting and Economics, 44(1–2), 193–223.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Fama, E. F., &amp; Jensen, M. C. (1983). Separation of ownership and control. Journal of Law and Economics, 26(2), 301–325.</t>
+          <t>Dyreng, S. D., Hanlon, M., &amp; Maydew, E. L. (2008). Long-run corporate tax avoidance. The Accounting Review, 83(1), 61–82.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Fich, E. M., &amp; Shivdasani, A. (2006). Are busy boards effective monitors? Journal of Finance, 61(2), 689–724.</t>
+          <t>Edmans, A. (2011). Does the stock market fully value intangibles? Employee satisfaction and equity prices. Journal of Financial Economics, 101(3), 621–640.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Finkelstein, S. (1992). Power in top management teams: Dimensions, measurement, and validation. Academy of Management Journal, 35(3), 505–538.</t>
+          <t>Fama, E. F., &amp; Jensen, M. C. (1983). Separation of ownership and control. Journal of Law and Economics, 26(2), 301–325.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Flesch, R. (1948). A new readability yardstick. Journal of Applied Psychology, 32(3), 221–233.</t>
+          <t>Fich, E. M., &amp; Shivdasani, A. (2006). Are busy boards effective monitors? Journal of Finance, 61(2), 689–724.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Francis, J., LaFond, R., Olsson, P. M., &amp; Schipper, K. (2004). Costs of equity and earnings attributes. The Accounting Review, 79(4), 967–1010.</t>
+          <t>Finkelstein, S. (1992). Power in top management teams: Dimensions, measurement, and validation. Academy of Management Journal, 35(3), 505–538.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Givoly, D., &amp; Hayn, C. (2000). The changing time-series properties of earnings, cash flows and accruals. Journal of Accounting and Economics, 29(3), 287–320.</t>
+          <t>Flesch, R. (1948). A new readability yardstick. Journal of Applied Psychology, 32(3), 221–233.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Givoly, D., &amp; Palmon, D. (1982). Timeliness of annual earnings announcements: Some empirical evidence. The Accounting Review, 57(3), 486–508.</t>
+          <t>Francis, J., LaFond, R., Olsson, P. M., &amp; Schipper, K. (2004). Costs of equity and earnings attributes. The Accounting Review, 79(4), 967–1010.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Gompers, P., Ishii, J., &amp; Metrick, A. (2003). Corporate governance and equity prices. Quarterly Journal of Economics, 118(1), 107–156.</t>
+          <t>Givoly, D., &amp; Hayn, C. (2000). The changing time-series properties of earnings, cash flows and accruals. Journal of Accounting and Economics, 29(3), 287–320.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Gray, R., Kouhy, R., &amp; Lavers, S. (1995). Corporate social and environmental reporting. Accounting, Auditing &amp; Accountability Journal, 8(2), 47–77.</t>
+          <t>Givoly, D., &amp; Palmon, D. (1982). Timeliness of annual earnings announcements: Some empirical evidence. The Accounting Review, 57(3), 486–508.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Gunning, R. (1952). The technique of clear writing. New York: McGraw-Hill.</t>
+          <t>Gompers, P., Ishii, J., &amp; Metrick, A. (2003). Corporate governance and equity prices. Quarterly Journal of Economics, 118(1), 107–156.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Hackston, D., &amp; Milne, M. J. (1996). Some determinants of social and environmental disclosures in New Zealand companies. Accounting, Auditing &amp; Accountability Journal, 9(1), 77–108.</t>
+          <t>Gray, R., Kouhy, R., &amp; Lavers, S. (1995). Corporate social and environmental reporting. Accounting, Auditing &amp; Accountability Journal, 8(2), 47–77.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Hall, B. H., Jaffe, A., &amp; Trajtenberg, M. (2005). Market value and patent citations. RAND Journal of Economics, 36(1), 16–38.</t>
+          <t>Gunning, R. (1952). The technique of clear writing. New York: McGraw-Hill.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Hanlon, M., &amp; Heitzman, S. (2010). A review of tax research. Journal of Accounting and Economics, 50(2–3), 127–178.</t>
+          <t>Hackston, D., &amp; Milne, M. J. (1996). Some determinants of social and environmental disclosures in New Zealand companies. Accounting, Auditing &amp; Accountability Journal, 9(1), 77–108.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Healy, P. M. (1985). The effect of bonus schemes on accounting decisions. Journal of Accounting and Economics, 7(1–3), 85–107.</t>
+          <t>Hall, B. H., Jaffe, A., &amp; Trajtenberg, M. (2005). Market value and patent citations. RAND Journal of Economics, 36(1), 16–38.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Healy, P. M., &amp; Palepu, K. G. (2001). Information asymmetry, corporate disclosure, and the capital markets. Journal of Accounting and Economics, 31(1–3), 405–440.</t>
+          <t>Hanlon, M., &amp; Heitzman, S. (2010). A review of tax research. Journal of Accounting and Economics, 50(2–3), 127–178.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Henry, E. (2008). Are investors influenced by how earnings press releases are written? Journal of Business Communication, 45(4), 363–407.</t>
+          <t>Healy, P. M. (1985). The effect of bonus schemes on accounting decisions. Journal of Accounting and Economics, 7(1–3), 85–107.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Hribar, P., &amp; Yang, H. (2016). CEO overconfidence and management forecasting. Contemporary Accounting Research, 33(1), 204–227.</t>
+          <t>Healy, P. M., &amp; Palepu, K. G. (2001). Information asymmetry, corporate disclosure, and the capital markets. Journal of Accounting and Economics, 31(1–3), 405–440.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Huang, X., Teoh, S. H., &amp; Zhang, Y. (2014). Tone management. The Accounting Review, 89(3), 1083–1113.</t>
+          <t>Henry, E. (2008). Are investors influenced by how earnings press releases are written? Journal of Business Communication, 45(4), 363–407.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Hutton, A. P., Marcus, A. J., &amp; Tehranian, H. (2009). Opaque financial reports, R², and crash risk. Journal of Financial Economics, 94(1), 67–86.</t>
+          <t>Hou, K., &amp; Robinson, D. T. (2006). Industry concentration and average stock returns. Journal of Finance, 61(4), 1927–1956.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Jian, M., &amp; Wong, T. J. (2010). Propping through related party transactions. Review of Accounting Studies, 15(1), 70–105.</t>
+          <t>Hribar, P., &amp; Yang, H. (2016). CEO overconfidence and management forecasting. Contemporary Accounting Research, 33(1), 204–227.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Jiang, G., Lee, C. M. C., &amp; Yue, H. (2010). Tunneling through intercorporate loans: The China experience. Journal of Financial Economics, 98(1), 1–20.</t>
+          <t>Huang, X., Teoh, S. H., &amp; Zhang, Y. (2014). Tone management. The Accounting Review, 89(3), 1083–1113.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Jin, L., &amp; Myers, S. C. (2006). R² around the world: New theory and new tests. Journal of Financial Economics, 79(2), 257–292.</t>
+          <t>Hutton, A. P., Marcus, A. J., &amp; Tehranian, H. (2009). Opaque financial reports, R², and crash risk. Journal of Financial Economics, 94(1), 67–86.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Jones, J. J. (1991). Earnings management during import relief investigations. Journal of Accounting Research, 29(2), 193–228.</t>
+          <t>Jian, M., &amp; Wong, T. J. (2010). Propping through related party transactions. Review of Accounting Studies, 15(1), 70–105.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Kincaid, J. P., Fishburne, R. P., Rogers, R. L., &amp; Chissom, B. S. (1975). Derivation of new readability formulas for Navy enlisted personnel. Naval Technical Training Command, Research Branch Report 8-75.</t>
+          <t>Jiang, G., Lee, C. M. C., &amp; Yue, H. (2010). Tunneling through intercorporate loans: The China experience. Journal of Financial Economics, 98(1), 1–20.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Klein, A. (2002). Audit committee, board of director characteristics, and earnings management. Journal of Accounting and Economics, 33(3), 375–400.</t>
+          <t>Jin, L., &amp; Myers, S. C. (2006). R² around the world: New theory and new tests. Journal of Financial Economics, 79(2), 257–292.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Knechel, W. R., &amp; Payne, J. L. (2001). Additional evidence on audit report lag. Auditing: A Journal of Practice &amp; Theory, 20(1), 137–146.</t>
+          <t>Jones, J. J. (1991). Earnings management during import relief investigations. Journal of Accounting Research, 29(2), 193–228.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Kothari, S. P., Leone, A. J., &amp; Wasley, C. E. (2005). Performance matched discretionary accrual measures. Journal of Accounting and Economics, 39(1), 163–197.</t>
+          <t>Kim, J.-B., Li, Y., &amp; Zhang, L. (2011). Corporate tax avoidance and stock price crash risk: Firm-level analysis. Journal of Financial Economics, 100(3), 639–662.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>La Porta, R., Lopez-de-Silanes, F., &amp; Shleifer, A. (1999). Corporate ownership around the world. Journal of Finance, 54(2), 471–517.</t>
+          <t>Kincaid, J. P., Fishburne, R. P., Rogers, R. L., &amp; Chissom, B. S. (1975). Derivation of new readability formulas for Navy enlisted personnel. Naval Technical Training Command, Research Branch Report 8-75.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Lang, M., &amp; Lundholm, R. (1993). Cross-sectional determinants of analyst ratings of corporate disclosures. Journal of Accounting Research, 31(2), 246–271.</t>
+          <t>Klein, A. (2002). Audit committee, board of director characteristics, and earnings management. Journal of Accounting and Economics, 33(3), 375–400.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Leuz, C., Nanda, D., &amp; Wysocki, P. D. (2003). Earnings management and investor protection: An international comparison. Journal of Financial Economics, 69(3), 505–527.</t>
+          <t>Knechel, W. R., &amp; Payne, J. L. (2001). Additional evidence on audit report lag. Auditing: A Journal of Practice &amp; Theory, 20(1), 137–146.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Li, F. (2008). Annual report readability, current earnings, and earnings persistence. Journal of Accounting and Economics, 45(2–3), 221–247.</t>
+          <t>Kothari, S. P., Leone, A. J., &amp; Wasley, C. E. (2005). Performance matched discretionary accrual measures. Journal of Accounting and Economics, 39(1), 163–197.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Li, F. (2010). The information content of forward-looking statements in corporate filings: A naïve Bayesian machine learning approach. Journal of Accounting Research, 48(5), 1049–1102.</t>
+          <t>La Porta, R., Lopez-de-Silanes, F., &amp; Shleifer, A. (1999). Corporate ownership around the world. Journal of Finance, 54(2), 471–517.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Lintner, J. (1956). Distribution of incomes of corporations among dividends, retained earnings, and taxes. American Economic Review, 46(2), 97–113.</t>
+          <t>Lang, M., &amp; Lundholm, R. (1993). Cross-sectional determinants of analyst ratings of corporate disclosures. Journal of Accounting Research, 31(2), 246–271.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Loughran, T., &amp; McDonald, B. (2011). When is a liability not a liability? Textual analysis, dictionaries, and 10-Ks. Journal of Finance, 66(1), 35–65.</t>
+          <t>Lerner, A. P. (1934). The concept of monopoly and the measurement of monopoly power. Review of Economic Studies, 1(3), 157–175.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Loughran, T., &amp; McDonald, B. (2014). Measuring readability in financial disclosures. Journal of Finance, 69(4), 1643–1671.</t>
+          <t>Lesmond, D. A., Ogden, J. P., &amp; Trzcinka, C. A. (1999). A new estimate of transaction costs. Review of Financial Studies, 12(5), 1113–1141.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Malmendier, U., &amp; Tate, G. (2005). CEO overconfidence and corporate investment. Journal of Finance, 60(6), 2661–2700.</t>
+          <t>Leuz, C., Nanda, D., &amp; Wysocki, P. D. (2003). Earnings management and investor protection: An international comparison. Journal of Financial Economics, 69(3), 505–527.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Malmendier, U., &amp; Tate, G. (2008). Who makes acquisitions? CEO overconfidence and the market's reaction. Journal of Financial Economics, 89(1), 20–43.</t>
+          <t>Li, F. (2008). Annual report readability, current earnings, and earnings persistence. Journal of Accounting and Economics, 45(2–3), 221–247.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Malmendier, U., Tate, G., &amp; Yan, J. (2011). Overconfidence and early-life experiences: The effect of managerial traits on corporate financial policies. Journal of Finance, 66(5), 1687–1733.</t>
+          <t>Li, F. (2010). The information content of forward-looking statements in corporate filings: A naïve Bayesian machine learning approach. Journal of Accounting Research, 48(5), 1049–1102.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Matsumoto, D. A. (2002). Management's incentives to avoid negative earnings surprises. The Accounting Review, 77(3), 483–514.</t>
+          <t>Lintner, J. (1956). Distribution of incomes of corporations among dividends, retained earnings, and taxes. American Economic Review, 46(2), 97–113.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>McLaughlin, G. H. (1969). SMOG grading: A new readability formula. Journal of Reading, 12(8), 639–646.</t>
+          <t>Loughran, T., &amp; McDonald, B. (2011). When is a liability not a liability? Textual analysis, dictionaries, and 10-Ks. Journal of Finance, 66(1), 35–65.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>McNichols, M. F. (2002). Discussion of the quality of accruals and earnings: The role of accrual estimation errors. The Accounting Review, 77(Supplement), 61–69.</t>
+          <t>Loughran, T., &amp; McDonald, B. (2014). Measuring readability in financial disclosures. Journal of Finance, 69(4), 1643–1671.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Morck, R., Shleifer, A., &amp; Vishny, R. W. (1988). Management ownership and market valuation: An empirical analysis. Journal of Financial Economics, 20, 293–315.</t>
+          <t>Malmendier, U., &amp; Tate, G. (2005). CEO overconfidence and corporate investment. Journal of Finance, 60(6), 2661–2700.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Murphy, K. J., &amp; Zimmerman, J. L. (1993). Financial performance surrounding CEO turnover. Journal of Accounting and Economics, 16(1–3), 273–315.</t>
+          <t>Malmendier, U., &amp; Tate, G. (2008). Who makes acquisitions? CEO overconfidence and the market's reaction. Journal of Financial Economics, 89(1), 20–43.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Myers, J. N., Myers, L. A., &amp; Omer, T. C. (2003). Exploring the term of the auditor–client relationship and the quality of earnings. The Accounting Review, 78(3), 779–799.</t>
+          <t>Malmendier, U., Tate, G., &amp; Yan, J. (2011). Overconfidence and early-life experiences: The effect of managerial traits on corporate financial policies. Journal of Finance, 66(5), 1687–1733.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Piotroski, J. D. (2000). Value investing: The use of historical financial statement information to separate winners from losers. Journal of Accounting Research, 38(Supplement), 1–41.</t>
+          <t>Matsumoto, D. A. (2002). Management's incentives to avoid negative earnings surprises. The Accounting Review, 77(3), 483–514.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Prawitt, D. F., Smith, J. L., &amp; Wood, D. A. (2009). Internal audit quality and earnings management. The Accounting Review, 84(4), 1255–1280.</t>
+          <t>McLaughlin, G. H. (1969). SMOG grading: A new readability formula. Journal of Reading, 12(8), 639–646.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Richardson, S. (2006). Over-investment of free cash flow. Review of Accounting Studies, 11(2–3), 159–189.</t>
+          <t>McNichols, M. F. (2002). Discussion of the quality of accruals and earnings: The role of accrual estimation errors. The Accounting Review, 77(Supplement), 61–69.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Roychowdhury, S. (2006). Earnings management through real activities manipulation. Journal of Accounting and Economics, 42(3), 335–370.</t>
+          <t>Morck, R., Shleifer, A., &amp; Vishny, R. W. (1988). Management ownership and market valuation: An empirical analysis. Journal of Financial Economics, 20, 293–315.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Shleifer, A., &amp; Vishny, R. W. (1986). Large shareholders and corporate control. Journal of Political Economy, 94(3), 461–488.</t>
+          <t>Morck, R., Yeung, B., &amp; Yu, W. (2000). The information content of stock markets: Why do emerging markets have synchronous stock price movements? Journal of Financial Economics, 58(1–2), 215–260.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Simnett, R., Vanstraelen, A., &amp; Chua, W. F. (2009). Assurance on sustainability reports: An international comparison. The Accounting Review, 84(3), 937–967.</t>
+          <t>Murphy, K. J., &amp; Zimmerman, J. L. (1993). Financial performance surrounding CEO turnover. Journal of Accounting and Economics, 16(1–3), 273–315.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Simunic, D. A. (1980). The pricing of audit services: Theory and evidence. Journal of Accounting Research, 18(1), 161–190.</t>
+          <t>Myers, J. N., Myers, L. A., &amp; Omer, T. C. (2003). Exploring the term of the auditor–client relationship and the quality of earnings. The Accounting Review, 78(3), 779–799.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Sloan, R. G. (1996). Do stock prices fully reflect information in accruals and cash flows about future earnings? The Accounting Review, 71(3), 289–315.</t>
+          <t>Peress, J. (2010). Product market competition, insider trading, and stock market efficiency. Journal of Finance, 65(1), 1–43.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Tetlock, P. C. (2007). Giving content to investor sentiment: The role of media in the stock market. Journal of Finance, 62(3), 1139–1168.</t>
+          <t>Piotroski, J. D. (2000). Value investing: The use of historical financial statement information to separate winners from losers. Journal of Accounting Research, 38(Supplement), 1–41.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Vafeas, N. (1999). Board meeting frequency and firm performance. Journal of Financial Economics, 53(1), 113–142.</t>
+          <t>Prawitt, D. F., Smith, J. L., &amp; Wood, D. A. (2009). Internal audit quality and earnings management. The Accounting Review, 84(4), 1255–1280.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>Richardson, S. (2006). Over-investment of free cash flow. Review of Accounting Studies, 11(2–3), 159–189.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Roychowdhury, S. (2006). Earnings management through real activities manipulation. Journal of Accounting and Economics, 42(3), 335–370.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Shleifer, A., &amp; Vishny, R. W. (1986). Large shareholders and corporate control. Journal of Political Economy, 94(3), 461–488.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Simnett, R., Vanstraelen, A., &amp; Chua, W. F. (2009). Assurance on sustainability reports: An international comparison. The Accounting Review, 84(3), 937–967.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Simunic, D. A. (1980). The pricing of audit services: Theory and evidence. Journal of Accounting Research, 18(1), 161–190.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Sloan, R. G. (1996). Do stock prices fully reflect information in accruals and cash flows about future earnings? The Accounting Review, 71(3), 289–315.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Tetlock, P. C. (2007). Giving content to investor sentiment: The role of media in the stock market. Journal of Finance, 62(3), 1139–1168.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Vafeas, N. (1999). Board meeting frequency and firm performance. Journal of Financial Economics, 53(1), 113–142.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
           <t>Yermack, D. (1996). Higher market valuation of companies with a small board of directors. Journal of Financial Economics, 40(2), 185–211.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A95"/>
+  <autoFilter ref="A1:A103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>